--- a/Design/Excel/ET/Datas/Game/Stages.xlsx
+++ b/Design/Excel/ET/Datas/Game/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C531FA-80FD-48A0-ACD6-CC1F967E921A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BDEF19-6D38-4919-A0CA-DBE994E86AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="2" r:id="rId1"/>
@@ -75,15 +75,15 @@
     <t>(array#sep=,),int</t>
   </si>
   <si>
-    <t>20001,20001</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SubLevel</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>20001,20002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" s="5"/>
     </row>
@@ -635,7 +635,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="5"/>
     </row>

--- a/Design/Excel/ET/Datas/Game/Stages.xlsx
+++ b/Design/Excel/ET/Datas/Game/Stages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BDEF19-6D38-4919-A0CA-DBE994E86AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A170C6-92DD-40CC-AAE8-813FA5909082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -640,43 +640,83 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
       <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="5"/>
+      <c r="B8" s="5">
+        <v>5</v>
+      </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="5"/>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="5"/>
+      <c r="B10" s="5">
+        <v>7</v>
+      </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">

--- a/Design/Excel/ET/Datas/Game/Stages.xlsx
+++ b/Design/Excel/ET/Datas/Game/Stages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A170C6-92DD-40CC-AAE8-813FA5909082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90F4E76-A2F6-4721-8264-5AB7834F17DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7220" yWindow="2570" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -84,6 +84,66 @@
   </si>
   <si>
     <t>20001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20003</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20003,20004</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20004</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20002,20003</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropIds</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">掉落 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30001;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30002;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30003;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30005;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30004;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30006;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;10000|30007;20000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=|),(array#sep=;),int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -545,8 +605,8 @@
     <col min="2" max="2" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.90625" customWidth="1"/>
     <col min="4" max="5" width="12.7265625" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" customWidth="1"/>
-    <col min="7" max="7" width="17.81640625" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -566,7 +626,9 @@
       <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
@@ -585,7 +647,9 @@
       <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
@@ -604,7 +668,9 @@
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -621,7 +687,9 @@
       <c r="F4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
@@ -635,9 +703,11 @@
         <v>1</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
@@ -651,9 +721,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
@@ -667,9 +739,11 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
@@ -683,9 +757,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
@@ -699,9 +775,11 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
@@ -715,9 +793,11 @@
         <v>2</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
